--- a/outputs/cv_summary.xlsx
+++ b/outputs/cv_summary.xlsx
@@ -525,22 +525,22 @@
         <v>3.008309710682015</v>
       </c>
       <c r="J2" t="n">
-        <v>0.7961885217887942</v>
+        <v>1.847404854971347</v>
       </c>
       <c r="K2" t="n">
-        <v>2.502175162369948</v>
+        <v>3.008309710682015</v>
       </c>
       <c r="L2" t="n">
-        <v>1.649181842079371</v>
+        <v>2.427857282826681</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>VAR_SV_macro_pca</t>
+          <t>VAR_SV_only</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>ARIMAX_NS_macro_pca_iv1</t>
+          <t>VAR_SV_only</t>
         </is>
       </c>
     </row>
@@ -584,10 +584,10 @@
         <v>2.37166813772766</v>
       </c>
       <c r="K3" t="n">
-        <v>2.67294167012565</v>
+        <v>2.451398075521608</v>
       </c>
       <c r="L3" t="n">
-        <v>2.522304903926655</v>
+        <v>2.411533106624634</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -596,7 +596,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>VAR_SV_only_iv1</t>
+          <t>ARIMAX_NS_macro_pca_iv1</t>
         </is>
       </c>
     </row>
@@ -637,13 +637,13 @@
         <v>3.057172935951666</v>
       </c>
       <c r="J4" t="n">
-        <v>2.680832399279703</v>
+        <v>2.270533974613536</v>
       </c>
       <c r="K4" t="n">
-        <v>1.392528322879856</v>
+        <v>1.612535918565556</v>
       </c>
       <c r="L4" t="n">
-        <v>2.03668036107978</v>
+        <v>1.941534946589546</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -693,13 +693,13 @@
         <v>3.498978943198353</v>
       </c>
       <c r="J5" t="n">
-        <v>1.531862289275031</v>
+        <v>1.214903591889314</v>
       </c>
       <c r="K5" t="n">
-        <v>1.869981173324486</v>
+        <v>3.366939097224857</v>
       </c>
       <c r="L5" t="n">
-        <v>1.700921731299758</v>
+        <v>2.290921344557086</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
